--- a/public/downloads/register-closing-checklist.xlsx
+++ b/public/downloads/register-closing-checklist.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
   <si>
     <t>レジ締めチェック表</t>
   </si>
   <si>
-    <t>黄色の所に入力すると、灰色の所が自動で計算されます。日付ごとにシートをコピーして使ってください。</t>
+    <t>黄色の所に入力すると、灰色の所が自動で計算されます。日付ごとにシートをコピーして使い、精算レシートといっしょに保管しましょう。</t>
   </si>
   <si>
     <t>日付</t>
@@ -28,6 +28,15 @@
     <t>締めた人／確かめた人</t>
   </si>
   <si>
+    <t>0. 締める前に（POSレジの画面で。済んだら「済」を選ぶ）</t>
+  </si>
+  <si>
+    <t>取り消し・返品・訂正の伝票に問題がない</t>
+  </si>
+  <si>
+    <t>送られていない会計データがない（通知が出ていないか）</t>
+  </si>
+  <si>
     <t>1. 現金を数える（金種表）</t>
   </si>
   <si>
@@ -73,25 +82,40 @@
     <t>決済の管理画面</t>
   </si>
   <si>
+    <t>差</t>
+  </si>
+  <si>
     <t>クレジットカード</t>
   </si>
   <si>
     <t>QRコード決済</t>
   </si>
   <si>
+    <t>営業中に金庫などへ移した現金</t>
+  </si>
+  <si>
+    <t>電子マネー</t>
+  </si>
+  <si>
     <t>数えた現金の合計（A）</t>
   </si>
   <si>
-    <t>電子マネー</t>
-  </si>
-  <si>
-    <t>差があれば、支払い方法の登録まちがいを確かめる</t>
+    <t>その他（商品券など）</t>
+  </si>
+  <si>
+    <t>商品券・クーポン券は現金とまぜずに分けて数えます。</t>
+  </si>
+  <si>
+    <t>「差」が0でなければ、支払い方法の登録まちがいを確かめる</t>
   </si>
   <si>
     <t>4. 差額が出たら、上から順に確かめる（済んだら「済」を選ぶ）</t>
   </si>
   <si>
-    <t>金種ごとに数え直した</t>
+    <t>金種ごとに数え直した（お札の重なり、硬貨の積み方、商品券がまざっていないか）</t>
+  </si>
+  <si>
+    <t>金庫などへ移した現金も数えた（交代のときの伝え忘れはないか）</t>
   </si>
   <si>
     <t>開店時の釣り銭（B）が、いつもの金額と同じ</t>
@@ -100,10 +124,16 @@
     <t>営業中の入金・出金（D・E）を、すべて記録した</t>
   </si>
   <si>
-    <t>返品・取り消しの会計で、現金を戻したか確かめた</t>
-  </si>
-  <si>
-    <t>キャッシュレスの会計を「現金」で登録していない</t>
+    <t>キャッシュレスの会計を「現金」で登録していない（3の表の「差」が0か）</t>
+  </si>
+  <si>
+    <t>会計忘れ・二重の会計・取り消し忘れがない（返品のときに現金を戻したかも）</t>
+  </si>
+  <si>
+    <t>値引き・クーポンがレジに入っている（口頭で値引きして、入れ忘れていないか）</t>
+  </si>
+  <si>
+    <t>差額が、どれかの会計のお釣りと同じ金額ではない（お釣りの渡し間違いの手がかり）</t>
   </si>
   <si>
     <t>差額の理由・気づいたこと</t>
@@ -112,10 +142,10 @@
     <t>5. 店じまい</t>
   </si>
   <si>
-    <t>売上金を店内（レジ・金庫）に残していない</t>
-  </si>
-  <si>
-    <t>翌日の釣り銭を用意した（金額は右へ）</t>
+    <t>翌日の釣り銭を残した（金額は右へ。毎日同じ金額に決めておくと迷いません）</t>
+  </si>
+  <si>
+    <t>売上金を取り出した（A－翌日の釣り銭。右に自動で出ます）</t>
   </si>
   <si>
     <t>表・裏の出入口と、小さな窓の鍵を閉めた</t>
@@ -132,7 +162,7 @@
     <numFmt numFmtId="164" formatCode="#,##0&quot;円&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;枚&quot;"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -166,6 +196,10 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <name val="Yu Gothic"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Yu Gothic"/>
     </font>
@@ -232,12 +266,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -259,20 +296,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC0392B"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -617,15 +657,16 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="4" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="7" width="16" customWidth="1"/>
+    <col min="6" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -633,7 +674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -643,6 +684,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -662,360 +704,480 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="7" t="s">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+      <c r="B10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
         <v>10000</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="11">
-        <f>A7*B7</f>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
+      <c r="B11" s="11"/>
+      <c r="C11" s="12">
+        <f>A11*B11</f>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
         <v>5000</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="11">
-        <f>A8*B8</f>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+      <c r="B12" s="11"/>
+      <c r="C12" s="12">
+        <f>A12*B12</f>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
         <v>2000</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="11">
-        <f>A9*B9</f>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
+      <c r="B13" s="11"/>
+      <c r="C13" s="12">
+        <f>A13*B13</f>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
         <v>1000</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="11">
-        <f>A10*B10</f>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="13">
-        <f>F6+F7+F8-F9</f>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
+      <c r="B14" s="11"/>
+      <c r="C14" s="12">
+        <f>A14*B14</f>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="14">
+        <f>F10+F11+F12-F13</f>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="10">
         <v>500</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="11">
-        <f>A11*B11</f>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="13">
-        <f>C17-F10</f>
-      </c>
-      <c r="G11" s="14">
-        <f>IF(F11=0,"合っています",IF(F11&gt;0,"多い（現金が多い）","少ない（現金が足りない）"))</f>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
+      <c r="B15" s="11"/>
+      <c r="C15" s="12">
+        <f>A15*B15</f>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="14">
+        <f>C22-F14</f>
+      </c>
+      <c r="G15" s="15">
+        <f>IF(F15=0,"合っています",IF(F15&gt;0,"多い（現金が多い）","少ない（現金が足りない）"))</f>
+      </c>
+      <c r="H15" s="15"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="10">
         <v>100</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="11">
-        <f>A12*B12</f>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
+      <c r="B16" s="11"/>
+      <c r="C16" s="12">
+        <f>A16*B16</f>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
         <v>50</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="11">
-        <f>A13*B13</f>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="9">
+      <c r="B17" s="11"/>
+      <c r="C17" s="12">
+        <f>A17*B17</f>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
         <v>10</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="11">
-        <f>A14*B14</f>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="9">
+      <c r="B18" s="11"/>
+      <c r="C18" s="12">
+        <f>A18*B18</f>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="10">
         <v>5</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="11">
-        <f>A15*B15</f>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="9">
+      <c r="B19" s="11"/>
+      <c r="C19" s="12">
+        <f>A19*B19</f>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="12">
+        <f>F19-G19</f>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="10">
         <v>1</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="11">
-        <f>A16*B16</f>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="13">
-        <f>SUM(C7:C16)</f>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-    </row>
-    <row r="18" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="B20" s="11"/>
+      <c r="C20" s="12">
+        <f>A20*B20</f>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="12">
+        <f>F20-G20</f>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="B21" s="16"/>
+      <c r="C21" s="9"/>
+      <c r="E21" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="12">
+        <f>F21-G21</f>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="B22" s="17"/>
+      <c r="C22" s="14">
+        <f>SUM(C11:C21)</f>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="12">
+        <f>F22-G22</f>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="E23" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>32</v>
       </c>
     </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="8"/>
+      <c r="A31" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="7" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
+      <c r="A33" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G39" s="9"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G40" s="14">
+        <f>IF(G39="","",C22-G39)</f>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A2:G2"/>
+  <mergeCells count="22">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A27:G28"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A35:H36"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A43:H43"/>
   </mergeCells>
-  <conditionalFormatting sqref="F11:G11">
+  <conditionalFormatting sqref="F15:G15">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$F$11&lt;&gt;0</formula>
+      <formula>$F$15&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="F21:F25">
+  <conditionalFormatting sqref="H19:H22">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>H19&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="F26:F33">
       <formula1>"済,－"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F31:F33">
+    <dataValidation type="list" allowBlank="1" sqref="F39:F41">
+      <formula1>"済,－"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F6:F7">
       <formula1>"済,－"</formula1>
     </dataValidation>
   </dataValidations>
